--- a/consent_forms/044_new_hire_worker_liability_waiver_form--consent_forms.xlsx
+++ b/consent_forms/044_new_hire_worker_liability_waiver_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'i_have_read_and_agree_to_the_terms_and_conditions'}</t>
+          <t>i_have_read_and_agree_to_the_terms_and_conditions</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'I have read and agree to the terms and conditions'}</t>
+          <t>I have read and agree to the terms and conditions</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'i_have_not_read_and_do_not_agree_to_the_terms_and_conditions'}</t>
+          <t>i_have_not_read_and_do_not_agree_to_the_terms_and_conditions</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'I have not read and do not agree to the terms and conditions'}</t>
+          <t>I have not read and do not agree to the terms and conditions</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'self-inflicted'}</t>
+          <t>self-inflicted</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Self-Inflicted'}</t>
+          <t>Self-Inflicted</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'others'}</t>
+          <t>others</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Others'}</t>
+          <t>Others</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'signature'}</t>
+          <t>signature</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Signature'}</t>
+          <t>Signature</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'no_signature'}</t>
+          <t>no_signature</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'No Signature'}</t>
+          <t>No Signature</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'i_understand_the_terms_and_conditions'}</t>
+          <t>i_understand_the_terms_and_conditions</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'I understand the terms and conditions'}</t>
+          <t>I understand the terms and conditions</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'i_do_not_understand_the_terms_and_conditions'}</t>
+          <t>i_do_not_understand_the_terms_and_conditions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'I do not understand the terms and conditions'}</t>
+          <t>I do not understand the terms and conditions</t>
         </is>
       </c>
     </row>
